--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/MARYLAND_2022.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2022/MARYLAND_2022.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D573"/>
+  <dimension ref="A1:D567"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Asientos</t>
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C4">
@@ -421,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rincón de Romos</t>
+          <t>Rincón De Romos</t>
         </is>
       </c>
       <c r="C5">
@@ -434,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Candelaria</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Carmen</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Escárcega</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -592,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Arriaga</t>
@@ -605,9 +665,14 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bejucal de Ocampo</t>
+          <t>Bejucal De Ocampo</t>
         </is>
       </c>
       <c r="C18">
@@ -618,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -631,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -644,9 +719,14 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chiapa de Corzo</t>
+          <t>Chiapa De Corzo</t>
         </is>
       </c>
       <c r="C21">
@@ -657,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Chicomuselo</t>
@@ -670,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -683,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Escuintla</t>
@@ -696,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -709,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -722,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Huixtán</t>
@@ -735,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -748,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Jiquipilas</t>
@@ -761,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -774,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -787,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -800,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C33">
@@ -813,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -826,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Nicolás Ruíz</t>
@@ -839,9 +989,14 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ocozocoautla de Espinosa</t>
+          <t>Ocozocoautla De Espinosa</t>
         </is>
       </c>
       <c r="C36">
@@ -852,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Pantelhó</t>
@@ -865,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C38">
@@ -878,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>San Fernando</t>
@@ -891,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -904,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Simojovel</t>
@@ -917,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Suchiapa</t>
@@ -930,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -943,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -956,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -969,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -982,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -995,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Tuxtla Gutiérrez</t>
@@ -1008,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -1021,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Tzimol</t>
@@ -1034,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -1047,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -1060,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Villaflores</t>
@@ -1073,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1104,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -1117,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Rosales</t>
@@ -1130,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1161,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -1174,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Monclova</t>
@@ -1187,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>San Juan de Sabinas</t>
+          <t>San Juan De Sabinas</t>
         </is>
       </c>
       <c r="C62">
@@ -1200,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1213,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1228,7 +1513,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1244,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1257,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1270,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1283,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Cuajimalpa de Morelos</t>
+          <t>Cuajimalpa De Morelos</t>
         </is>
       </c>
       <c r="C69">
@@ -1296,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1309,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1322,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1335,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1348,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -1361,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1374,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1387,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1400,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1413,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -1426,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1457,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1470,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Mezquital</t>
@@ -1483,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1498,12 +1873,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C85">
@@ -1514,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C86">
@@ -1527,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Amanalco</t>
@@ -1540,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -1553,9 +1943,14 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C89">
@@ -1566,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Atlacomulco</t>
@@ -1579,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Atlautla</t>
@@ -1592,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -1605,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1618,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -1631,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -1644,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Donato Guerra</t>
@@ -1657,9 +2087,14 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C97">
@@ -1670,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -1683,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Huixquilucan</t>
@@ -1696,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Ixtapaluca</t>
@@ -1709,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C101">
@@ -1722,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -1735,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Jilotepec</t>
@@ -1748,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Jilotzingo</t>
@@ -1761,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -1774,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Luvianos</t>
@@ -1787,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Malinalco</t>
@@ -1800,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -1813,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C109">
@@ -1826,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1839,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Nicolás Romero</t>
@@ -1852,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Otumba</t>
@@ -1865,6 +2375,11 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>Ozumba</t>
@@ -1878,9 +2393,14 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C114">
@@ -1891,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Santo Tomás</t>
@@ -1904,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Tecámac</t>
@@ -1917,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -1930,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -1943,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -1956,6 +2501,11 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>Teoloyucan</t>
@@ -1969,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Tepetlixpa</t>
@@ -1982,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Tepotzotlán</t>
@@ -1995,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Texcaltitlán</t>
@@ -2008,6 +2573,11 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -2021,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C125">
@@ -2034,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Tlatlaya</t>
@@ -2047,6 +2627,11 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -2060,9 +2645,14 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Valle de Bravo</t>
+          <t>Valle De Bravo</t>
         </is>
       </c>
       <c r="C128">
@@ -2073,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -2086,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Xonacatlán</t>
@@ -2099,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Zacazonapan</t>
@@ -2112,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2143,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Acámbaro</t>
@@ -2156,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -2169,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C136">
@@ -2182,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Apaseo el Grande</t>
+          <t>Apaseo El Grande</t>
         </is>
       </c>
       <c r="C137">
@@ -2195,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -2208,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -2221,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -2234,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Cuerámaro</t>
@@ -2247,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -2260,9 +2915,14 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jaral del Progreso</t>
+          <t>Jaral Del Progreso</t>
         </is>
       </c>
       <c r="C143">
@@ -2273,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -2286,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>León</t>
@@ -2299,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>Moroleón</t>
@@ -2312,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -2325,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Salvatierra</t>
@@ -2338,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>San Diego de la Unión</t>
+          <t>San Diego De La Unión</t>
         </is>
       </c>
       <c r="C149">
@@ -2351,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>San Felipe</t>
@@ -2364,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C151">
@@ -2377,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Tarimoro</t>
@@ -2390,9 +3095,14 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C153">
@@ -2403,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Xichú</t>
@@ -2416,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -2429,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2449,7 +3174,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C157">
@@ -2460,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -2473,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C159">
@@ -2486,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Alpoyeca</t>
@@ -2499,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -2512,9 +3257,14 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Atlamajalcingo del Monte</t>
+          <t>Atlamajalcingo Del Monte</t>
         </is>
       </c>
       <c r="C162">
@@ -2525,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -2538,9 +3293,14 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C164">
@@ -2551,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -2564,9 +3329,14 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C166">
@@ -2577,9 +3347,14 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Coahuayutla de José María Izazaga</t>
+          <t>Coahuayutla De José María Izazaga</t>
         </is>
       </c>
       <c r="C167">
@@ -2590,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -2603,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -2616,9 +3401,14 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C170">
@@ -2629,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Cuajinicuilapa</t>
@@ -2642,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Cualác</t>
@@ -2655,9 +3455,14 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C173">
@@ -2668,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>General Canuto A. Neri</t>
@@ -2681,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Huamuxtitlán</t>
@@ -2694,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Igualapa</t>
@@ -2707,9 +3527,14 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C177">
@@ -2720,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -2733,9 +3563,14 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>La Unión de Isidoro Montes de Oca</t>
+          <t>La Unión De Isidoro Montes De Oca</t>
         </is>
       </c>
       <c r="C179">
@@ -2746,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -2759,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -2772,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -2785,6 +3635,11 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
           <t>Olinalá</t>
@@ -2798,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -2811,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Pedro Ascencio Alquisiras</t>
@@ -2824,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>Pungarabato</t>
@@ -2837,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -2850,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -2863,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -2876,9 +3761,14 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C190">
@@ -2889,9 +3779,14 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Tepecoacuilco de Trujano</t>
+          <t>Tepecoacuilco De Trujano</t>
         </is>
       </c>
       <c r="C191">
@@ -2902,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Tetipac</t>
@@ -2915,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Tlacoapa</t>
@@ -2928,9 +3833,14 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Tlalixtaquilla de Maldonado</t>
+          <t>Tlalixtaquilla De Maldonado</t>
         </is>
       </c>
       <c r="C194">
@@ -2941,9 +3851,14 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C195">
@@ -2954,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -2967,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Xochihuehuetlán</t>
@@ -2980,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>Xochistlahuaca</t>
@@ -2993,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Zapotitlán Tablas</t>
@@ -3006,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -3019,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3050,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Actopan</t>
@@ -3063,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Apan</t>
@@ -3076,9 +4031,14 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C205">
@@ -3089,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Calnali</t>
@@ -3102,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Cardonal</t>
@@ -3115,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Chapulhuacán</t>
@@ -3128,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Chilcuautla</t>
@@ -3141,9 +4121,14 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Cuautepec de Hinojosa</t>
+          <t>Cuautepec De Hinojosa</t>
         </is>
       </c>
       <c r="C210">
@@ -3154,6 +4139,11 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -3167,9 +4157,14 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Huejutla de Reyes</t>
+          <t>Huejutla De Reyes</t>
         </is>
       </c>
       <c r="C212">
@@ -3180,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -3193,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -3206,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -3219,9 +4229,14 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Molango de Escamilla</t>
+          <t>Molango De Escamilla</t>
         </is>
       </c>
       <c r="C216">
@@ -3232,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>Nicolás Flores</t>
@@ -3245,9 +4265,14 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C218">
@@ -3258,9 +4283,14 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Progreso de Obregón</t>
+          <t>Progreso De Obregón</t>
         </is>
       </c>
       <c r="C219">
@@ -3271,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>San Agustín Metzquititlán</t>
@@ -3284,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>San Bartolo Tutotepec</t>
@@ -3297,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Tasquillo</t>
@@ -3310,9 +4355,14 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Tepehuacán de Guerrero</t>
+          <t>Tepehuacán De Guerrero</t>
         </is>
       </c>
       <c r="C223">
@@ -3323,9 +4373,14 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Tepeji del Río de Ocampo</t>
+          <t>Tepeji Del Río De Ocampo</t>
         </is>
       </c>
       <c r="C224">
@@ -3336,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Tianguistengo</t>
@@ -3349,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Tlahuiltepa</t>
@@ -3362,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Tlanchinol</t>
@@ -3375,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Tlaxcoapan</t>
@@ -3388,9 +4463,14 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C229">
@@ -3401,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Xochicoatlán</t>
@@ -3414,9 +4499,14 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Zacualtipán de Ángeles</t>
+          <t>Zacualtipán De Ángeles</t>
         </is>
       </c>
       <c r="C231">
@@ -3427,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3458,9 +4553,14 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Encarnación de Díaz</t>
+          <t>Encarnación De Díaz</t>
         </is>
       </c>
       <c r="C234">
@@ -3471,6 +4571,11 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -3484,9 +4589,14 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C236">
@@ -3497,9 +4607,14 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>San Cristóbal de la Barranca</t>
+          <t>San Cristóbal De La Barranca</t>
         </is>
       </c>
       <c r="C237">
@@ -3510,9 +4625,14 @@
       </c>
     </row>
     <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>San Martín de Bolaños</t>
+          <t>San Martín De Bolaños</t>
         </is>
       </c>
       <c r="C238">
@@ -3523,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Teocaltiche</t>
@@ -3536,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -3549,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -3562,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Tototlán</t>
@@ -3575,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Villa Hidalgo</t>
@@ -3588,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -3601,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Zapotiltic</t>
@@ -3614,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3645,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Apatzingán</t>
@@ -3658,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -3671,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Charo</t>
@@ -3684,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Churumuco</t>
@@ -3697,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -3710,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Cuitzeo</t>
@@ -3723,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -3736,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Huetamo</t>
@@ -3749,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Irimbo</t>
@@ -3762,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Lagunillas</t>
@@ -3775,6 +4985,11 @@
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>Lázaro Cárdenas</t>
@@ -3788,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -3801,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -3814,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Paracho</t>
@@ -3827,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -3840,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Puruándiro</t>
@@ -3853,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Senguio</t>
@@ -3866,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -3879,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -3892,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Tingüindín</t>
@@ -3905,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Tlalpujahua</t>
@@ -3918,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Tumbiscatío</t>
@@ -3931,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -3944,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Tzintzuntzan</t>
@@ -3957,6 +5237,11 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
           <t>Uruapan</t>
@@ -3970,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -3983,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -3996,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -4009,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4040,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -4053,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -4066,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -4079,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Ocuituco</t>
@@ -4092,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Temixco</t>
@@ -4105,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Temoac</t>
@@ -4118,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Yautepec</t>
@@ -4131,9 +5471,14 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Zacualpan de Amilpas</t>
+          <t>Zacualpan De Amilpas</t>
         </is>
       </c>
       <c r="C285">
@@ -4144,6 +5489,11 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4175,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Linares</t>
@@ -4188,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Monterrey</t>
@@ -4201,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>San Pedro Garza García</t>
@@ -4214,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4245,9 +5615,14 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C293">
@@ -4258,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Ayotzintepec</t>
@@ -4271,9 +5651,14 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Fresnillo de Trujano</t>
+          <t>Fresnillo De Trujano</t>
         </is>
       </c>
       <c r="C295">
@@ -4284,9 +5669,14 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C296">
@@ -4297,9 +5687,14 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C297">
@@ -4310,9 +5705,14 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C298">
@@ -4323,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>La Compañía</t>
@@ -4336,9 +5741,14 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Mazatlán Villa de Flores</t>
+          <t>Mazatlán Villa De Flores</t>
         </is>
       </c>
       <c r="C300">
@@ -4349,9 +5759,14 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C301">
@@ -4362,9 +5777,14 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Mixistlán de la Reforma</t>
+          <t>Mixistlán De La Reforma</t>
         </is>
       </c>
       <c r="C302">
@@ -4375,9 +5795,14 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C303">
@@ -4388,9 +5813,14 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C304">
@@ -4401,9 +5831,14 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Reforma de Pineda</t>
+          <t>Reforma De Pineda</t>
         </is>
       </c>
       <c r="C305">
@@ -4414,6 +5849,11 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -4427,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>San Andrés Cabecera Nueva</t>
@@ -4440,6 +5885,11 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
           <t>San Andrés Dinicuiti</t>
@@ -4453,9 +5903,14 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>San Antonio de la Cal</t>
+          <t>San Antonio De La Cal</t>
         </is>
       </c>
       <c r="C309">
@@ -4466,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>San Carlos Yautepec</t>
@@ -4479,6 +5939,11 @@
       </c>
     </row>
     <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B311" t="inlineStr">
         <is>
           <t>San Felipe Usila</t>
@@ -4492,6 +5957,11 @@
       </c>
     </row>
     <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B312" t="inlineStr">
         <is>
           <t>San Francisco Chapulapa</t>
@@ -4505,6 +5975,11 @@
       </c>
     </row>
     <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B313" t="inlineStr">
         <is>
           <t>San Francisco Tlapancingo</t>
@@ -4518,6 +5993,11 @@
       </c>
     </row>
     <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B314" t="inlineStr">
         <is>
           <t>San Jerónimo Taviche</t>
@@ -4531,6 +6011,11 @@
       </c>
     </row>
     <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B315" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -4544,6 +6029,11 @@
       </c>
     </row>
     <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B316" t="inlineStr">
         <is>
           <t>San Juan Colorado</t>
@@ -4557,6 +6047,11 @@
       </c>
     </row>
     <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B317" t="inlineStr">
         <is>
           <t>San Juan Lalana</t>
@@ -4570,6 +6065,11 @@
       </c>
     </row>
     <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B318" t="inlineStr">
         <is>
           <t>San Juan Mazatlán</t>
@@ -4583,6 +6083,11 @@
       </c>
     </row>
     <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B319" t="inlineStr">
         <is>
           <t>San Juan Ozolotepec</t>
@@ -4596,6 +6101,11 @@
       </c>
     </row>
     <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B320" t="inlineStr">
         <is>
           <t>San Juan Tamazola</t>
@@ -4609,6 +6119,11 @@
       </c>
     </row>
     <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B321" t="inlineStr">
         <is>
           <t>San Lorenzo</t>
@@ -4622,6 +6137,11 @@
       </c>
     </row>
     <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B322" t="inlineStr">
         <is>
           <t>San Luis Amatlán</t>
@@ -4635,6 +6155,11 @@
       </c>
     </row>
     <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B323" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -4648,6 +6173,11 @@
       </c>
     </row>
     <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B324" t="inlineStr">
         <is>
           <t>San Miguel Amatitlán</t>
@@ -4661,6 +6191,11 @@
       </c>
     </row>
     <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B325" t="inlineStr">
         <is>
           <t>San Miguel Chicahua</t>
@@ -4674,6 +6209,11 @@
       </c>
     </row>
     <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B326" t="inlineStr">
         <is>
           <t>San Miguel Soyaltepec</t>
@@ -4687,6 +6227,11 @@
       </c>
     </row>
     <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B327" t="inlineStr">
         <is>
           <t>San Miguel Tequixtepec</t>
@@ -4700,6 +6245,11 @@
       </c>
     </row>
     <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B328" t="inlineStr">
         <is>
           <t>San Miguel Tlacamama</t>
@@ -4713,6 +6263,11 @@
       </c>
     </row>
     <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B329" t="inlineStr">
         <is>
           <t>San Pedro Amuzgos</t>
@@ -4726,6 +6281,11 @@
       </c>
     </row>
     <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B330" t="inlineStr">
         <is>
           <t>San Pedro Atoyac</t>
@@ -4739,6 +6299,11 @@
       </c>
     </row>
     <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B331" t="inlineStr">
         <is>
           <t>San Pedro Pochutla</t>
@@ -4752,6 +6317,11 @@
       </c>
     </row>
     <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B332" t="inlineStr">
         <is>
           <t>Santa Catarina Mechoacán</t>
@@ -4765,6 +6335,11 @@
       </c>
     </row>
     <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B333" t="inlineStr">
         <is>
           <t>Santa María Alotepec</t>
@@ -4778,6 +6353,11 @@
       </c>
     </row>
     <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B334" t="inlineStr">
         <is>
           <t>Santa María Apazco</t>
@@ -4791,6 +6371,11 @@
       </c>
     </row>
     <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B335" t="inlineStr">
         <is>
           <t>Santa María Colotepec</t>
@@ -4804,6 +6389,11 @@
       </c>
     </row>
     <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B336" t="inlineStr">
         <is>
           <t>Santa María Huazolotitlán</t>
@@ -4817,6 +6407,11 @@
       </c>
     </row>
     <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B337" t="inlineStr">
         <is>
           <t>Santa María Ipalapa</t>
@@ -4830,6 +6425,11 @@
       </c>
     </row>
     <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B338" t="inlineStr">
         <is>
           <t>Santa María Peñoles</t>
@@ -4843,6 +6443,11 @@
       </c>
     </row>
     <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B339" t="inlineStr">
         <is>
           <t>Santa María Tecomavaca</t>
@@ -4856,6 +6461,11 @@
       </c>
     </row>
     <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B340" t="inlineStr">
         <is>
           <t>Santa María Tlalixtac</t>
@@ -4869,6 +6479,11 @@
       </c>
     </row>
     <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B341" t="inlineStr">
         <is>
           <t>Santa María Tonameca</t>
@@ -4882,6 +6497,11 @@
       </c>
     </row>
     <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B342" t="inlineStr">
         <is>
           <t>Santa María Yucuhiti</t>
@@ -4895,6 +6515,11 @@
       </c>
     </row>
     <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B343" t="inlineStr">
         <is>
           <t>Santa María Zacatepec</t>
@@ -4908,6 +6533,11 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B344" t="inlineStr">
         <is>
           <t>Santiago Choápam</t>
@@ -4921,6 +6551,11 @@
       </c>
     </row>
     <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B345" t="inlineStr">
         <is>
           <t>Santiago Jamiltepec</t>
@@ -4934,6 +6569,11 @@
       </c>
     </row>
     <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B346" t="inlineStr">
         <is>
           <t>Santiago Jocotepec</t>
@@ -4947,6 +6587,11 @@
       </c>
     </row>
     <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B347" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -4960,6 +6605,11 @@
       </c>
     </row>
     <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B348" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -4973,6 +6623,11 @@
       </c>
     </row>
     <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B349" t="inlineStr">
         <is>
           <t>Santiago Tamazola</t>
@@ -4986,6 +6641,11 @@
       </c>
     </row>
     <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B350" t="inlineStr">
         <is>
           <t>Santiago Texcalcingo</t>
@@ -4999,6 +6659,11 @@
       </c>
     </row>
     <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B351" t="inlineStr">
         <is>
           <t>Santiago Textitlán</t>
@@ -5012,6 +6677,11 @@
       </c>
     </row>
     <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B352" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -5025,9 +6695,14 @@
       </c>
     </row>
     <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Tamazulápam del Espíritu Santo</t>
+          <t>Tamazulápam Del Espíritu Santo</t>
         </is>
       </c>
       <c r="C353">
@@ -5038,9 +6713,14 @@
       </c>
     </row>
     <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C354">
@@ -5051,9 +6731,14 @@
       </c>
     </row>
     <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Villa de Tututepec de Melchor Ocampo</t>
+          <t>Villa De Tututepec De Melchor Ocampo</t>
         </is>
       </c>
       <c r="C355">
@@ -5064,9 +6749,14 @@
       </c>
     </row>
     <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Villa de Zaachila</t>
+          <t>Villa De Zaachila</t>
         </is>
       </c>
       <c r="C356">
@@ -5077,6 +6767,11 @@
       </c>
     </row>
     <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B357" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5108,6 +6803,11 @@
       </c>
     </row>
     <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B359" t="inlineStr">
         <is>
           <t>Acatlán</t>
@@ -5121,6 +6821,11 @@
       </c>
     </row>
     <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
           <t>Ahuacatlán</t>
@@ -5134,6 +6839,11 @@
       </c>
     </row>
     <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B361" t="inlineStr">
         <is>
           <t>Ahuazotepec</t>
@@ -5147,6 +6857,11 @@
       </c>
     </row>
     <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B362" t="inlineStr">
         <is>
           <t>Aljojuca</t>
@@ -5160,6 +6875,11 @@
       </c>
     </row>
     <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B363" t="inlineStr">
         <is>
           <t>Atempan</t>
@@ -5173,6 +6893,11 @@
       </c>
     </row>
     <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B364" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -5186,6 +6911,11 @@
       </c>
     </row>
     <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B365" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -5199,6 +6929,11 @@
       </c>
     </row>
     <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B366" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -5212,6 +6947,11 @@
       </c>
     </row>
     <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B367" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -5225,6 +6965,11 @@
       </c>
     </row>
     <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B368" t="inlineStr">
         <is>
           <t>Chiconcuautla</t>
@@ -5238,6 +6983,11 @@
       </c>
     </row>
     <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B369" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -5251,6 +7001,11 @@
       </c>
     </row>
     <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B370" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -5264,6 +7019,11 @@
       </c>
     </row>
     <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B371" t="inlineStr">
         <is>
           <t>Chilchotla</t>
@@ -5277,6 +7037,11 @@
       </c>
     </row>
     <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B372" t="inlineStr">
         <is>
           <t>Chinantla</t>
@@ -5290,9 +7055,14 @@
       </c>
     </row>
     <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Cuayuca de Andrade</t>
+          <t>Cuayuca De Andrade</t>
         </is>
       </c>
       <c r="C373">
@@ -5303,6 +7073,11 @@
       </c>
     </row>
     <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B374" t="inlineStr">
         <is>
           <t>Cuyoaco</t>
@@ -5316,6 +7091,11 @@
       </c>
     </row>
     <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B375" t="inlineStr">
         <is>
           <t>Domingo Arenas</t>
@@ -5329,6 +7109,11 @@
       </c>
     </row>
     <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B376" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -5342,6 +7127,11 @@
       </c>
     </row>
     <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B377" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -5355,6 +7145,11 @@
       </c>
     </row>
     <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B378" t="inlineStr">
         <is>
           <t>Hermenegildo Galeana</t>
@@ -5368,6 +7163,11 @@
       </c>
     </row>
     <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B379" t="inlineStr">
         <is>
           <t>Honey</t>
@@ -5381,6 +7181,11 @@
       </c>
     </row>
     <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B380" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -5394,6 +7199,11 @@
       </c>
     </row>
     <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B381" t="inlineStr">
         <is>
           <t>Huauchinango</t>
@@ -5407,9 +7217,14 @@
       </c>
     </row>
     <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C382">
@@ -5420,6 +7235,11 @@
       </c>
     </row>
     <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B383" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -5433,6 +7253,11 @@
       </c>
     </row>
     <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B384" t="inlineStr">
         <is>
           <t>Hueytamalco</t>
@@ -5446,6 +7271,11 @@
       </c>
     </row>
     <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B385" t="inlineStr">
         <is>
           <t>Hueytlalpan</t>
@@ -5459,6 +7289,11 @@
       </c>
     </row>
     <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B386" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -5472,9 +7307,14 @@
       </c>
     </row>
     <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C387">
@@ -5485,6 +7325,11 @@
       </c>
     </row>
     <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B388" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -5498,6 +7343,11 @@
       </c>
     </row>
     <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B389" t="inlineStr">
         <is>
           <t>Jopala</t>
@@ -5511,6 +7361,11 @@
       </c>
     </row>
     <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B390" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -5524,6 +7379,11 @@
       </c>
     </row>
     <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B391" t="inlineStr">
         <is>
           <t>Ocotepec</t>
@@ -5537,6 +7397,11 @@
       </c>
     </row>
     <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B392" t="inlineStr">
         <is>
           <t>Pahuatlán</t>
@@ -5550,6 +7415,11 @@
       </c>
     </row>
     <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B393" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -5563,6 +7433,11 @@
       </c>
     </row>
     <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B394" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -5576,6 +7451,11 @@
       </c>
     </row>
     <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B395" t="inlineStr">
         <is>
           <t>Quimixtlán</t>
@@ -5589,6 +7469,11 @@
       </c>
     </row>
     <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B396" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -5602,6 +7487,11 @@
       </c>
     </row>
     <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B397" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -5615,6 +7505,11 @@
       </c>
     </row>
     <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B398" t="inlineStr">
         <is>
           <t>San Pablo Anicano</t>
@@ -5628,6 +7523,11 @@
       </c>
     </row>
     <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B399" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -5641,6 +7541,11 @@
       </c>
     </row>
     <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B400" t="inlineStr">
         <is>
           <t>San Pedro Yeloixtlahuaca</t>
@@ -5654,6 +7559,11 @@
       </c>
     </row>
     <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B401" t="inlineStr">
         <is>
           <t>Santa Isabel Cholula</t>
@@ -5667,6 +7577,11 @@
       </c>
     </row>
     <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B402" t="inlineStr">
         <is>
           <t>Tecamachalco</t>
@@ -5680,6 +7595,11 @@
       </c>
     </row>
     <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B403" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -5693,6 +7613,11 @@
       </c>
     </row>
     <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B404" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -5706,9 +7631,14 @@
       </c>
     </row>
     <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Tepanco de López</t>
+          <t>Tepanco De López</t>
         </is>
       </c>
       <c r="C405">
@@ -5719,6 +7649,11 @@
       </c>
     </row>
     <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B406" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -5732,6 +7667,11 @@
       </c>
     </row>
     <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B407" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -5745,6 +7685,11 @@
       </c>
     </row>
     <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B408" t="inlineStr">
         <is>
           <t>Tianguismanalco</t>
@@ -5758,6 +7703,11 @@
       </c>
     </row>
     <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B409" t="inlineStr">
         <is>
           <t>Tilapa</t>
@@ -5771,9 +7721,14 @@
       </c>
     </row>
     <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C410">
@@ -5784,6 +7739,11 @@
       </c>
     </row>
     <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B411" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -5797,6 +7757,11 @@
       </c>
     </row>
     <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B412" t="inlineStr">
         <is>
           <t>Tlapanalá</t>
@@ -5810,6 +7775,11 @@
       </c>
     </row>
     <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B413" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -5823,6 +7793,11 @@
       </c>
     </row>
     <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B414" t="inlineStr">
         <is>
           <t>Tochtepec</t>
@@ -5836,6 +7811,11 @@
       </c>
     </row>
     <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B415" t="inlineStr">
         <is>
           <t>Tulcingo</t>
@@ -5849,6 +7829,11 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -5862,6 +7847,11 @@
       </c>
     </row>
     <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
           <t>Xochiapulco</t>
@@ -5875,6 +7865,11 @@
       </c>
     </row>
     <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>Xochitlán Todos Santos</t>
@@ -5888,6 +7883,11 @@
       </c>
     </row>
     <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
           <t>Zacapala</t>
@@ -5901,6 +7901,11 @@
       </c>
     </row>
     <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B420" t="inlineStr">
         <is>
           <t>Zacapoaxtla</t>
@@ -5914,6 +7919,11 @@
       </c>
     </row>
     <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B421" t="inlineStr">
         <is>
           <t>Zautla</t>
@@ -5927,6 +7937,11 @@
       </c>
     </row>
     <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B422" t="inlineStr">
         <is>
           <t>Total</t>
@@ -5947,7 +7962,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C423">
@@ -5958,9 +7973,14 @@
       </c>
     </row>
     <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C424">
@@ -5971,9 +7991,14 @@
       </c>
     </row>
     <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C425">
@@ -5984,9 +8009,14 @@
       </c>
     </row>
     <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Pinal de Amoles</t>
+          <t>Pinal De Amoles</t>
         </is>
       </c>
       <c r="C426">
@@ -5997,6 +8027,11 @@
       </c>
     </row>
     <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B427" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -6010,6 +8045,11 @@
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B428" t="inlineStr">
         <is>
           <t>Tequisquiapan</t>
@@ -6023,6 +8063,11 @@
       </c>
     </row>
     <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B429" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6054,6 +8099,11 @@
       </c>
     </row>
     <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B431" t="inlineStr">
         <is>
           <t>José María Morelos</t>
@@ -6067,6 +8117,11 @@
       </c>
     </row>
     <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B432" t="inlineStr">
         <is>
           <t>Othón P. Blanco</t>
@@ -6080,6 +8135,11 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B433" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6111,6 +8171,11 @@
       </c>
     </row>
     <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B435" t="inlineStr">
         <is>
           <t>Aquismón</t>
@@ -6124,9 +8189,14 @@
       </c>
     </row>
     <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Ciudad del Maíz</t>
+          <t>Ciudad Del Maíz</t>
         </is>
       </c>
       <c r="C436">
@@ -6137,6 +8207,11 @@
       </c>
     </row>
     <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B437" t="inlineStr">
         <is>
           <t>Ciudad Valles</t>
@@ -6150,6 +8225,11 @@
       </c>
     </row>
     <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B438" t="inlineStr">
         <is>
           <t>Guadalcázar</t>
@@ -6163,6 +8243,11 @@
       </c>
     </row>
     <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B439" t="inlineStr">
         <is>
           <t>Rayón</t>
@@ -6176,6 +8261,11 @@
       </c>
     </row>
     <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B440" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -6189,6 +8279,11 @@
       </c>
     </row>
     <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B441" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -6202,9 +8297,14 @@
       </c>
     </row>
     <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C442">
@@ -6215,6 +8315,11 @@
       </c>
     </row>
     <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B443" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -6228,6 +8333,11 @@
       </c>
     </row>
     <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B444" t="inlineStr">
         <is>
           <t>Tamazunchale</t>
@@ -6241,6 +8351,11 @@
       </c>
     </row>
     <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B445" t="inlineStr">
         <is>
           <t>Tampamolón Corona</t>
@@ -6254,6 +8369,11 @@
       </c>
     </row>
     <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B446" t="inlineStr">
         <is>
           <t>Tamuín</t>
@@ -6267,6 +8387,11 @@
       </c>
     </row>
     <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B447" t="inlineStr">
         <is>
           <t>Tancanhuitz</t>
@@ -6280,9 +8405,14 @@
       </c>
     </row>
     <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Villa de la Paz</t>
+          <t>Villa De La Paz</t>
         </is>
       </c>
       <c r="C448">
@@ -6293,6 +8423,11 @@
       </c>
     </row>
     <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B449" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -6306,6 +8441,11 @@
       </c>
     </row>
     <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B450" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6337,6 +8477,11 @@
       </c>
     </row>
     <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B452" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -6350,6 +8495,11 @@
       </c>
     </row>
     <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B453" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -6363,6 +8513,11 @@
       </c>
     </row>
     <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B454" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6394,6 +8549,11 @@
       </c>
     </row>
     <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B456" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6425,6 +8585,11 @@
       </c>
     </row>
     <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B458" t="inlineStr">
         <is>
           <t>Cárdenas</t>
@@ -6438,6 +8603,11 @@
       </c>
     </row>
     <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B459" t="inlineStr">
         <is>
           <t>Centla</t>
@@ -6451,6 +8621,11 @@
       </c>
     </row>
     <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B460" t="inlineStr">
         <is>
           <t>Comalcalco</t>
@@ -6464,6 +8639,11 @@
       </c>
     </row>
     <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B461" t="inlineStr">
         <is>
           <t>Emiliano Zapata</t>
@@ -6477,6 +8657,11 @@
       </c>
     </row>
     <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B462" t="inlineStr">
         <is>
           <t>Huimanguillo</t>
@@ -6490,6 +8675,11 @@
       </c>
     </row>
     <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B463" t="inlineStr">
         <is>
           <t>Paraíso</t>
@@ -6503,6 +8693,11 @@
       </c>
     </row>
     <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B464" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6534,6 +8729,11 @@
       </c>
     </row>
     <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B466" t="inlineStr">
         <is>
           <t>Ciudad Madero</t>
@@ -6547,6 +8747,11 @@
       </c>
     </row>
     <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B467" t="inlineStr">
         <is>
           <t>El Mante</t>
@@ -6560,6 +8765,11 @@
       </c>
     </row>
     <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B468" t="inlineStr">
         <is>
           <t>Llera</t>
@@ -6573,6 +8783,11 @@
       </c>
     </row>
     <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B469" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -6586,6 +8801,11 @@
       </c>
     </row>
     <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B470" t="inlineStr">
         <is>
           <t>Miquihuana</t>
@@ -6599,6 +8819,11 @@
       </c>
     </row>
     <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B471" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -6612,6 +8837,11 @@
       </c>
     </row>
     <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B472" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -6625,6 +8855,11 @@
       </c>
     </row>
     <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B473" t="inlineStr">
         <is>
           <t>Tula</t>
@@ -6638,6 +8873,11 @@
       </c>
     </row>
     <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B474" t="inlineStr">
         <is>
           <t>Victoria</t>
@@ -6651,6 +8891,11 @@
       </c>
     </row>
     <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B475" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6682,6 +8927,11 @@
       </c>
     </row>
     <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B477" t="inlineStr">
         <is>
           <t>Calpulalpan</t>
@@ -6695,6 +8945,11 @@
       </c>
     </row>
     <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B478" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -6708,6 +8963,11 @@
       </c>
     </row>
     <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B479" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -6721,6 +8981,11 @@
       </c>
     </row>
     <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B480" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -6734,9 +8999,14 @@
       </c>
     </row>
     <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>San Pablo del Monte</t>
+          <t>San Pablo Del Monte</t>
         </is>
       </c>
       <c r="C481">
@@ -6747,6 +9017,11 @@
       </c>
     </row>
     <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B482" t="inlineStr">
         <is>
           <t>Tenancingo</t>
@@ -6760,6 +9035,11 @@
       </c>
     </row>
     <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B483" t="inlineStr">
         <is>
           <t>Teolocholco</t>
@@ -6773,6 +9053,11 @@
       </c>
     </row>
     <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B484" t="inlineStr">
         <is>
           <t>Terrenate</t>
@@ -6786,6 +9071,11 @@
       </c>
     </row>
     <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B485" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -6799,6 +9089,11 @@
       </c>
     </row>
     <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B486" t="inlineStr">
         <is>
           <t>Xaloztoc</t>
@@ -6812,6 +9107,11 @@
       </c>
     </row>
     <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B487" t="inlineStr">
         <is>
           <t>Xicohtzinco</t>
@@ -6825,6 +9125,11 @@
       </c>
     </row>
     <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B488" t="inlineStr">
         <is>
           <t>Total</t>
@@ -6856,6 +9161,11 @@
       </c>
     </row>
     <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B490" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -6869,6 +9179,11 @@
       </c>
     </row>
     <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B491" t="inlineStr">
         <is>
           <t>Angel R. Cabada</t>
@@ -6882,6 +9197,11 @@
       </c>
     </row>
     <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B492" t="inlineStr">
         <is>
           <t>Atoyac</t>
@@ -6895,6 +9215,11 @@
       </c>
     </row>
     <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B493" t="inlineStr">
         <is>
           <t>Atzacan</t>
@@ -6908,9 +9233,14 @@
       </c>
     </row>
     <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Boca del Río</t>
+          <t>Boca Del Río</t>
         </is>
       </c>
       <c r="C494">
@@ -6921,6 +9251,11 @@
       </c>
     </row>
     <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
           <t>Chiconquiaco</t>
@@ -6934,6 +9269,11 @@
       </c>
     </row>
     <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B496" t="inlineStr">
         <is>
           <t>Chicontepec</t>
@@ -6947,6 +9287,11 @@
       </c>
     </row>
     <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B497" t="inlineStr">
         <is>
           <t>Chocamán</t>
@@ -6960,6 +9305,11 @@
       </c>
     </row>
     <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B498" t="inlineStr">
         <is>
           <t>Coatepec</t>
@@ -6973,6 +9323,11 @@
       </c>
     </row>
     <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B499" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -6986,6 +9341,11 @@
       </c>
     </row>
     <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B500" t="inlineStr">
         <is>
           <t>Coatzintla</t>
@@ -6999,6 +9359,11 @@
       </c>
     </row>
     <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B501" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -7012,9 +9377,14 @@
       </c>
     </row>
     <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Cosamaloapan de Carpio</t>
+          <t>Cosamaloapan De Carpio</t>
         </is>
       </c>
       <c r="C502">
@@ -7025,6 +9395,11 @@
       </c>
     </row>
     <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B503" t="inlineStr">
         <is>
           <t>Coyutla</t>
@@ -7038,6 +9413,11 @@
       </c>
     </row>
     <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B504" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -7051,6 +9431,11 @@
       </c>
     </row>
     <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B505" t="inlineStr">
         <is>
           <t>Fortín</t>
@@ -7064,6 +9449,11 @@
       </c>
     </row>
     <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B506" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -7077,6 +9467,11 @@
       </c>
     </row>
     <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B507" t="inlineStr">
         <is>
           <t>Huayacocotla</t>
@@ -7090,9 +9485,14 @@
       </c>
     </row>
     <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Hueyapan de Ocampo</t>
+          <t>Hueyapan De Ocampo</t>
         </is>
       </c>
       <c r="C508">
@@ -7103,9 +9503,14 @@
       </c>
     </row>
     <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C509">
@@ -7116,9 +9521,14 @@
       </c>
     </row>
     <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Ixhuacán de los Reyes</t>
+          <t>Ixhuacán De Los Reyes</t>
         </is>
       </c>
       <c r="C510">
@@ -7129,9 +9539,14 @@
       </c>
     </row>
     <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Ixhuatlán de Madero</t>
+          <t>Ixhuatlán De Madero</t>
         </is>
       </c>
       <c r="C511">
@@ -7142,9 +9557,14 @@
       </c>
     </row>
     <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Ixhuatlán del Café</t>
+          <t>Ixhuatlán Del Café</t>
         </is>
       </c>
       <c r="C512">
@@ -7155,6 +9575,11 @@
       </c>
     </row>
     <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B513" t="inlineStr">
         <is>
           <t>Jalacingo</t>
@@ -7168,6 +9593,11 @@
       </c>
     </row>
     <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B514" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -7181,6 +9611,11 @@
       </c>
     </row>
     <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B515" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -7194,9 +9629,14 @@
       </c>
     </row>
     <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Juchique de Ferrer</t>
+          <t>Juchique De Ferrer</t>
         </is>
       </c>
       <c r="C516">
@@ -7207,6 +9647,11 @@
       </c>
     </row>
     <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B517" t="inlineStr">
         <is>
           <t>La Antigua</t>
@@ -7220,6 +9665,11 @@
       </c>
     </row>
     <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B518" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -7233,6 +9683,11 @@
       </c>
     </row>
     <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B519" t="inlineStr">
         <is>
           <t>Maltrata</t>
@@ -7246,6 +9701,11 @@
       </c>
     </row>
     <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B520" t="inlineStr">
         <is>
           <t>Manlio Fabio Altamirano</t>
@@ -7259,9 +9719,14 @@
       </c>
     </row>
     <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C521">
@@ -7272,6 +9737,11 @@
       </c>
     </row>
     <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B522" t="inlineStr">
         <is>
           <t>Miahuatlán</t>
@@ -7285,6 +9755,11 @@
       </c>
     </row>
     <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B523" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -7298,6 +9773,11 @@
       </c>
     </row>
     <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B524" t="inlineStr">
         <is>
           <t>Misantla</t>
@@ -7311,9 +9791,14 @@
       </c>
     </row>
     <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Mixtla de Altamirano</t>
+          <t>Mixtla De Altamirano</t>
         </is>
       </c>
       <c r="C525">
@@ -7324,6 +9809,11 @@
       </c>
     </row>
     <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B526" t="inlineStr">
         <is>
           <t>Moloacán</t>
@@ -7337,9 +9827,14 @@
       </c>
     </row>
     <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Nanchital de Lázaro Cárdenas del Río</t>
+          <t>Nanchital De Lázaro Cárdenas Del Río</t>
         </is>
       </c>
       <c r="C527">
@@ -7350,6 +9845,11 @@
       </c>
     </row>
     <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B528" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -7363,6 +9863,11 @@
       </c>
     </row>
     <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B529" t="inlineStr">
         <is>
           <t>Orizaba</t>
@@ -7376,6 +9881,11 @@
       </c>
     </row>
     <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B530" t="inlineStr">
         <is>
           <t>Otatitlán</t>
@@ -7389,6 +9899,11 @@
       </c>
     </row>
     <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B531" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -7402,9 +9917,14 @@
       </c>
     </row>
     <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Paso del Macho</t>
+          <t>Paso Del Macho</t>
         </is>
       </c>
       <c r="C532">
@@ -7415,6 +9935,11 @@
       </c>
     </row>
     <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B533" t="inlineStr">
         <is>
           <t>Platón Sánchez</t>
@@ -7428,6 +9953,11 @@
       </c>
     </row>
     <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B534" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -7441,6 +9971,11 @@
       </c>
     </row>
     <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B535" t="inlineStr">
         <is>
           <t>Río Blanco</t>
@@ -7454,6 +9989,11 @@
       </c>
     </row>
     <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B536" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -7467,6 +10007,11 @@
       </c>
     </row>
     <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B537" t="inlineStr">
         <is>
           <t>San Juan Evangelista</t>
@@ -7480,6 +10025,11 @@
       </c>
     </row>
     <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B538" t="inlineStr">
         <is>
           <t>Santiago Tuxtla</t>
@@ -7493,6 +10043,11 @@
       </c>
     </row>
     <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B539" t="inlineStr">
         <is>
           <t>Soledad Atzompa</t>
@@ -7506,6 +10061,11 @@
       </c>
     </row>
     <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B540" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -7519,6 +10079,11 @@
       </c>
     </row>
     <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B541" t="inlineStr">
         <is>
           <t>Teocelo</t>
@@ -7532,6 +10097,11 @@
       </c>
     </row>
     <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B542" t="inlineStr">
         <is>
           <t>Tepatlaxco</t>
@@ -7545,6 +10115,11 @@
       </c>
     </row>
     <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B543" t="inlineStr">
         <is>
           <t>Tepetlán</t>
@@ -7558,6 +10133,11 @@
       </c>
     </row>
     <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B544" t="inlineStr">
         <is>
           <t>Tezonapa</t>
@@ -7571,6 +10151,11 @@
       </c>
     </row>
     <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B545" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -7584,6 +10169,11 @@
       </c>
     </row>
     <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B546" t="inlineStr">
         <is>
           <t>Tihuatlán</t>
@@ -7597,6 +10187,11 @@
       </c>
     </row>
     <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B547" t="inlineStr">
         <is>
           <t>Tlachichilco</t>
@@ -7610,6 +10205,11 @@
       </c>
     </row>
     <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B548" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -7623,6 +10223,11 @@
       </c>
     </row>
     <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B549" t="inlineStr">
         <is>
           <t>Tres Valles</t>
@@ -7636,6 +10241,11 @@
       </c>
     </row>
     <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B550" t="inlineStr">
         <is>
           <t>Uxpanapa</t>
@@ -7649,6 +10259,11 @@
       </c>
     </row>
     <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B551" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -7662,6 +10277,11 @@
       </c>
     </row>
     <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B552" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -7675,6 +10295,11 @@
       </c>
     </row>
     <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B553" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -7688,6 +10313,11 @@
       </c>
     </row>
     <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B554" t="inlineStr">
         <is>
           <t>Yecuatla</t>
@@ -7701,6 +10331,11 @@
       </c>
     </row>
     <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B555" t="inlineStr">
         <is>
           <t>Zongolica</t>
@@ -7714,6 +10349,11 @@
       </c>
     </row>
     <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B556" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7745,6 +10385,11 @@
       </c>
     </row>
     <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B558" t="inlineStr">
         <is>
           <t>Valladolid</t>
@@ -7758,6 +10403,11 @@
       </c>
     </row>
     <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B559" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7789,9 +10439,14 @@
       </c>
     </row>
     <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Mezquital del Oro</t>
+          <t>Mezquital Del Oro</t>
         </is>
       </c>
       <c r="C561">
@@ -7802,6 +10457,11 @@
       </c>
     </row>
     <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B562" t="inlineStr">
         <is>
           <t>Tepetongo</t>
@@ -7815,9 +10475,14 @@
       </c>
     </row>
     <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C563">
@@ -7828,6 +10493,11 @@
       </c>
     </row>
     <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B564" t="inlineStr">
         <is>
           <t>Villa González Ortega</t>
@@ -7841,6 +10511,11 @@
       </c>
     </row>
     <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B565" t="inlineStr">
         <is>
           <t>Villanueva</t>
@@ -7854,6 +10529,11 @@
       </c>
     </row>
     <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B566" t="inlineStr">
         <is>
           <t>Total</t>
@@ -7877,41 +10557,6 @@
       </c>
       <c r="D567">
         <v>1</v>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 566,547</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>Mayo de 2023</t>
-        </is>
       </c>
     </row>
   </sheetData>
